--- a/masterProjectList.xlsx
+++ b/masterProjectList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben Hess\Documents\GitHub\btmhess.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F314AC2-2E54-402B-A1F3-9FC51BC2D75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CCF29D-8A4F-4B7E-8536-6926327DB759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46695" yWindow="3690" windowWidth="28800" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="127">
   <si>
     <t>Goldwing tractive battery</t>
   </si>
@@ -416,7 +416,7 @@
     <t>pics done</t>
   </si>
   <si>
-    <t>active</t>
+    <t>complete_in_use</t>
   </si>
 </sst>
 </file>
@@ -875,7 +875,7 @@
         <v>60</v>
       </c>
       <c r="H2">
-        <v>7590</v>
+        <v>4379.1499999999996</v>
       </c>
       <c r="I2" t="s">
         <v>126</v>
@@ -896,6 +896,9 @@
         <v>98</v>
       </c>
       <c r="O2" t="s">
+        <v>98</v>
+      </c>
+      <c r="P2" t="s">
         <v>98</v>
       </c>
     </row>
@@ -921,7 +924,25 @@
       <c r="G3">
         <v>28</v>
       </c>
+      <c r="H3">
+        <v>2336.87</v>
+      </c>
+      <c r="I3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" t="s">
+        <v>98</v>
+      </c>
+      <c r="L3" t="s">
+        <v>98</v>
+      </c>
       <c r="M3" t="s">
+        <v>98</v>
+      </c>
+      <c r="O3" t="s">
         <v>98</v>
       </c>
     </row>

--- a/masterProjectList.xlsx
+++ b/masterProjectList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben Hess\Documents\GitHub\btmhess.github.io\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\btmhess.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CCF29D-8A4F-4B7E-8536-6926327DB759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E6A64A-54E1-478C-931D-FCC53B407B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="11686" windowHeight="13763" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="128">
   <si>
     <t>Goldwing tractive battery</t>
   </si>
@@ -417,6 +417,9 @@
   </si>
   <si>
     <t>complete_in_use</t>
+  </si>
+  <si>
+    <t>active</t>
   </si>
 </sst>
 </file>
@@ -787,18 +790,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="44.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" customWidth="1"/>
-    <col min="13" max="14" width="10.28515625" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="44.265625" customWidth="1"/>
+    <col min="2" max="2" width="18.265625" customWidth="1"/>
+    <col min="3" max="3" width="21.265625" customWidth="1"/>
+    <col min="4" max="4" width="12.73046875" customWidth="1"/>
+    <col min="5" max="5" width="9.73046875" customWidth="1"/>
+    <col min="8" max="8" width="9.3984375" customWidth="1"/>
+    <col min="10" max="10" width="9.59765625" customWidth="1"/>
+    <col min="12" max="12" width="12.265625" customWidth="1"/>
+    <col min="13" max="14" width="10.265625" customWidth="1"/>
+    <col min="15" max="15" width="11.3984375" customWidth="1"/>
     <col min="16" max="16" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -945,6 +948,9 @@
       <c r="O3" t="s">
         <v>98</v>
       </c>
+      <c r="P3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
@@ -967,6 +973,18 @@
       </c>
       <c r="G4">
         <v>75</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4" t="s">
+        <v>127</v>
+      </c>
+      <c r="K4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L4" t="s">
+        <v>98</v>
       </c>
       <c r="M4" t="s">
         <v>98</v>

--- a/masterProjectList.xlsx
+++ b/masterProjectList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\btmhess.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E6A64A-54E1-478C-931D-FCC53B407B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2843220A-DDE1-4CF7-BFBB-82A363A0B59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="11686" windowHeight="13763" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="130">
   <si>
     <t>Goldwing tractive battery</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Battery discharge bucket</t>
   </si>
   <si>
-    <t>Quadwood</t>
-  </si>
-  <si>
     <t>Traxxas</t>
   </si>
   <si>
@@ -420,6 +417,15 @@
   </si>
   <si>
     <t>active</t>
+  </si>
+  <si>
+    <t>in email</t>
+  </si>
+  <si>
+    <t>complete_in_storage</t>
+  </si>
+  <si>
+    <t>Quadwood Go-Kart</t>
   </si>
 </sst>
 </file>
@@ -792,10 +798,10 @@
   <dimension ref="A1:P53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="44.265625" customWidth="1"/>
+    <col min="1" max="1" width="30.46484375" customWidth="1"/>
     <col min="2" max="2" width="18.265625" customWidth="1"/>
-    <col min="3" max="3" width="21.265625" customWidth="1"/>
-    <col min="4" max="4" width="12.73046875" customWidth="1"/>
+    <col min="3" max="3" width="10.1328125" customWidth="1"/>
+    <col min="4" max="4" width="7.73046875" customWidth="1"/>
     <col min="5" max="5" width="9.73046875" customWidth="1"/>
     <col min="8" max="8" width="9.3984375" customWidth="1"/>
     <col min="10" max="10" width="9.59765625" customWidth="1"/>
@@ -807,63 +813,63 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" t="s">
         <v>31</v>
       </c>
-      <c r="C1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>32</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H1" t="s">
         <v>33</v>
       </c>
-      <c r="G1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>34</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>35</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>36</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>37</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O1" t="s">
         <v>38</v>
       </c>
-      <c r="M1" t="s">
-        <v>124</v>
-      </c>
-      <c r="N1" t="s">
-        <v>125</v>
-      </c>
-      <c r="O1" t="s">
-        <v>39</v>
-      </c>
       <c r="P1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -881,28 +887,28 @@
         <v>4379.1499999999996</v>
       </c>
       <c r="I2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -910,10 +916,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3">
         <v>6</v>
@@ -931,36 +937,36 @@
         <v>2336.87</v>
       </c>
       <c r="I3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -978,27 +984,30 @@
         <v>100</v>
       </c>
       <c r="I4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M4" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+      <c r="P4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" t="s">
         <v>90</v>
       </c>
-      <c r="B5" t="s">
-        <v>91</v>
-      </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D5">
         <v>14</v>
@@ -1012,19 +1021,37 @@
       <c r="G5">
         <v>2</v>
       </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>125</v>
+      </c>
+      <c r="K5" t="s">
+        <v>97</v>
+      </c>
+      <c r="L5" t="s">
+        <v>97</v>
+      </c>
       <c r="M5" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+      <c r="N5" t="s">
+        <v>97</v>
+      </c>
+      <c r="P5" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>129</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D6">
         <v>15</v>
@@ -1038,19 +1065,37 @@
       <c r="G6">
         <v>8</v>
       </c>
+      <c r="H6">
+        <v>3786</v>
+      </c>
+      <c r="I6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K6" t="s">
+        <v>97</v>
+      </c>
+      <c r="L6" t="s">
+        <v>97</v>
+      </c>
       <c r="M6" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+      <c r="O6" t="s">
+        <v>97</v>
+      </c>
+      <c r="P6" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7">
         <v>19</v>
@@ -1065,18 +1110,18 @@
         <v>6</v>
       </c>
       <c r="M7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D8">
         <v>20</v>
@@ -1091,18 +1136,18 @@
         <v>16</v>
       </c>
       <c r="M8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D9">
         <v>21</v>
@@ -1117,18 +1162,18 @@
         <v>70</v>
       </c>
       <c r="M9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D10">
         <v>25</v>
@@ -1143,18 +1188,18 @@
         <v>16</v>
       </c>
       <c r="M10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" t="s">
         <v>99</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>100</v>
-      </c>
-      <c r="C11" t="s">
-        <v>101</v>
       </c>
       <c r="D11">
         <v>26</v>
@@ -1169,18 +1214,18 @@
         <v>400</v>
       </c>
       <c r="M11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D12">
         <v>28</v>
@@ -1195,18 +1240,18 @@
         <v>32</v>
       </c>
       <c r="M12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D13">
         <v>29</v>
@@ -1221,18 +1266,18 @@
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D14">
         <v>30</v>
@@ -1246,19 +1291,22 @@
       <c r="G14">
         <v>40</v>
       </c>
+      <c r="H14" t="s">
+        <v>127</v>
+      </c>
       <c r="M14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D15">
         <v>32</v>
@@ -1273,18 +1321,18 @@
         <v>16</v>
       </c>
       <c r="M15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D16">
         <v>35</v>
@@ -1299,18 +1347,18 @@
         <v>3</v>
       </c>
       <c r="M16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" t="s">
         <v>113</v>
       </c>
-      <c r="B17" t="s">
-        <v>114</v>
-      </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D17">
         <v>39</v>
@@ -1325,18 +1373,18 @@
         <v>1040</v>
       </c>
       <c r="M17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D18">
         <v>40</v>
@@ -1351,18 +1399,18 @@
         <v>16</v>
       </c>
       <c r="M18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" t="s">
         <v>111</v>
       </c>
-      <c r="B19" t="s">
-        <v>112</v>
-      </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D19">
         <v>41</v>
@@ -1377,18 +1425,18 @@
         <v>2</v>
       </c>
       <c r="M19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D20">
         <v>44</v>
@@ -1403,18 +1451,18 @@
         <v>2</v>
       </c>
       <c r="M20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21">
         <v>45</v>
@@ -1429,18 +1477,18 @@
         <v>1</v>
       </c>
       <c r="M21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D22">
         <v>46</v>
@@ -1455,18 +1503,18 @@
         <v>4</v>
       </c>
       <c r="M22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D23">
         <v>50</v>
@@ -1481,18 +1529,18 @@
         <v>6</v>
       </c>
       <c r="M23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" t="s">
         <v>109</v>
       </c>
-      <c r="B24" t="s">
-        <v>110</v>
-      </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D24">
         <v>54</v>
@@ -1507,18 +1555,18 @@
         <v>2</v>
       </c>
       <c r="M24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D25">
         <v>55</v>
@@ -1533,18 +1581,18 @@
         <v>3</v>
       </c>
       <c r="M25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" t="s">
         <v>107</v>
       </c>
-      <c r="B26" t="s">
-        <v>108</v>
-      </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D26">
         <v>56</v>
@@ -1559,7 +1607,7 @@
         <v>2</v>
       </c>
       <c r="M26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1567,10 +1615,10 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D27">
         <v>60</v>
@@ -1585,7 +1633,7 @@
         <v>16</v>
       </c>
       <c r="M27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1593,10 +1641,10 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D28">
         <v>65</v>
@@ -1611,18 +1659,18 @@
         <v>1</v>
       </c>
       <c r="M28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" t="s">
         <v>119</v>
       </c>
-      <c r="B29" t="s">
-        <v>120</v>
-      </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D29">
         <v>69</v>
@@ -1637,18 +1685,18 @@
         <v>2</v>
       </c>
       <c r="M29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D30">
         <v>70</v>
@@ -1663,18 +1711,18 @@
         <v>3</v>
       </c>
       <c r="M30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" t="s">
         <v>105</v>
       </c>
-      <c r="B31" t="s">
-        <v>106</v>
-      </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D31">
         <v>71</v>
@@ -1689,18 +1737,18 @@
         <v>4</v>
       </c>
       <c r="M31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" t="s">
         <v>117</v>
       </c>
-      <c r="B32" t="s">
-        <v>118</v>
-      </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D32">
         <v>73</v>
@@ -1715,18 +1763,18 @@
         <v>2</v>
       </c>
       <c r="M32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D33">
         <v>75</v>
@@ -1741,18 +1789,18 @@
         <v>4</v>
       </c>
       <c r="M33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D34">
         <v>80</v>
@@ -1767,18 +1815,18 @@
         <v>4</v>
       </c>
       <c r="M34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D35">
         <v>85</v>
@@ -1793,18 +1841,18 @@
         <v>2</v>
       </c>
       <c r="M35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D36">
         <v>90</v>
@@ -1819,18 +1867,18 @@
         <v>3</v>
       </c>
       <c r="M36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D37">
         <v>95</v>
@@ -1845,18 +1893,18 @@
         <v>40</v>
       </c>
       <c r="M37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D38">
         <v>100</v>
@@ -1871,18 +1919,18 @@
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D39">
         <v>110</v>
@@ -1897,18 +1945,18 @@
         <v>4</v>
       </c>
       <c r="M39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D40">
         <v>115</v>
@@ -1923,18 +1971,18 @@
         <v>2</v>
       </c>
       <c r="M40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D41">
         <v>120</v>
@@ -1949,18 +1997,18 @@
         <v>1</v>
       </c>
       <c r="M41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D42">
         <v>125</v>
@@ -1975,18 +2023,18 @@
         <v>4</v>
       </c>
       <c r="M42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D43">
         <v>130</v>
@@ -2001,18 +2049,18 @@
         <v>16</v>
       </c>
       <c r="M43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D44">
         <v>135</v>
@@ -2027,18 +2075,18 @@
         <v>6</v>
       </c>
       <c r="M44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" t="s">
         <v>94</v>
       </c>
-      <c r="B45" t="s">
-        <v>95</v>
-      </c>
       <c r="C45" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D45">
         <v>145</v>
@@ -2053,18 +2101,18 @@
         <v>520</v>
       </c>
       <c r="M45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D46">
         <v>150</v>
@@ -2079,18 +2127,18 @@
         <v>4</v>
       </c>
       <c r="M46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D47">
         <v>160</v>
@@ -2105,18 +2153,18 @@
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D48">
         <v>165</v>
@@ -2131,18 +2179,18 @@
         <v>2</v>
       </c>
       <c r="M48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D49">
         <v>170</v>
@@ -2157,35 +2205,35 @@
         <v>300</v>
       </c>
       <c r="M49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D50">
         <v>175</v>
       </c>
       <c r="M50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D51">
         <v>180</v>
@@ -2200,18 +2248,18 @@
         <v>3</v>
       </c>
       <c r="M51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D52">
         <v>185</v>
@@ -2226,18 +2274,18 @@
         <v>1</v>
       </c>
       <c r="M52" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D53">
         <v>190</v>
@@ -2252,7 +2300,7 @@
         <v>24</v>
       </c>
       <c r="M53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/masterProjectList.xlsx
+++ b/masterProjectList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\btmhess.github.io\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben Hess\Documents\GitHub\btmhess.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2843220A-DDE1-4CF7-BFBB-82A363A0B59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36598C6-ADC6-4B78-B0A4-ACBAC09BCE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="130">
   <si>
     <t>Goldwing tractive battery</t>
   </si>
@@ -796,18 +796,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P53"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.46484375" customWidth="1"/>
-    <col min="2" max="2" width="18.265625" customWidth="1"/>
-    <col min="3" max="3" width="10.1328125" customWidth="1"/>
-    <col min="4" max="4" width="7.73046875" customWidth="1"/>
-    <col min="5" max="5" width="9.73046875" customWidth="1"/>
-    <col min="8" max="8" width="9.3984375" customWidth="1"/>
-    <col min="10" max="10" width="9.59765625" customWidth="1"/>
-    <col min="12" max="12" width="12.265625" customWidth="1"/>
-    <col min="13" max="14" width="10.265625" customWidth="1"/>
-    <col min="15" max="15" width="11.3984375" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" customWidth="1"/>
+    <col min="13" max="14" width="10.28515625" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
     <col min="16" max="16" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1109,7 +1109,19 @@
       <c r="G7">
         <v>6</v>
       </c>
+      <c r="H7">
+        <v>285</v>
+      </c>
+      <c r="I7" t="s">
+        <v>125</v>
+      </c>
+      <c r="L7" t="s">
+        <v>97</v>
+      </c>
       <c r="M7" t="s">
+        <v>97</v>
+      </c>
+      <c r="O7" t="s">
         <v>97</v>
       </c>
     </row>

--- a/masterProjectList.xlsx
+++ b/masterProjectList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben Hess\Documents\GitHub\btmhess.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36598C6-ADC6-4B78-B0A4-ACBAC09BCE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B640D3D-C57C-4A63-98FA-AD61C03EE475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="130">
   <si>
     <t>Goldwing tractive battery</t>
   </si>
@@ -1124,6 +1124,9 @@
       <c r="O7" t="s">
         <v>97</v>
       </c>
+      <c r="P7" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">

--- a/masterProjectList.xlsx
+++ b/masterProjectList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben Hess\Documents\GitHub\btmhess.github.io\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\btmhess.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B640D3D-C57C-4A63-98FA-AD61C03EE475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E91FC0-6AC6-4134-BA3F-1CCF26BAB3C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="130">
   <si>
     <t>Goldwing tractive battery</t>
   </si>
@@ -796,18 +796,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" customWidth="1"/>
-    <col min="13" max="14" width="10.28515625" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="30.3984375" customWidth="1"/>
+    <col min="2" max="2" width="18.265625" customWidth="1"/>
+    <col min="3" max="3" width="10.1328125" customWidth="1"/>
+    <col min="4" max="4" width="7.73046875" customWidth="1"/>
+    <col min="5" max="5" width="9.73046875" customWidth="1"/>
+    <col min="8" max="8" width="9.3984375" customWidth="1"/>
+    <col min="10" max="10" width="9.59765625" customWidth="1"/>
+    <col min="12" max="12" width="12.265625" customWidth="1"/>
+    <col min="13" max="14" width="10.265625" customWidth="1"/>
+    <col min="15" max="15" width="11.3984375" customWidth="1"/>
     <col min="16" max="16" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1150,7 +1150,28 @@
       <c r="G8">
         <v>16</v>
       </c>
+      <c r="H8">
+        <v>1143</v>
+      </c>
+      <c r="I8" t="s">
+        <v>128</v>
+      </c>
+      <c r="J8" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" t="s">
+        <v>97</v>
+      </c>
+      <c r="L8" t="s">
+        <v>97</v>
+      </c>
       <c r="M8" t="s">
+        <v>97</v>
+      </c>
+      <c r="O8" t="s">
+        <v>97</v>
+      </c>
+      <c r="P8" t="s">
         <v>97</v>
       </c>
     </row>

--- a/masterProjectList.xlsx
+++ b/masterProjectList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\btmhess.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E91FC0-6AC6-4134-BA3F-1CCF26BAB3C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451AA615-3108-4DEA-ADE2-5490D5B8A2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="131">
   <si>
     <t>Goldwing tractive battery</t>
   </si>
@@ -426,6 +426,9 @@
   </si>
   <si>
     <t>Quadwood Go-Kart</t>
+  </si>
+  <si>
+    <t>complete_abandoned</t>
   </si>
 </sst>
 </file>
@@ -1197,6 +1200,21 @@
       <c r="G9">
         <v>70</v>
       </c>
+      <c r="H9">
+        <v>1000</v>
+      </c>
+      <c r="I9" t="s">
+        <v>130</v>
+      </c>
+      <c r="J9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" t="s">
+        <v>97</v>
+      </c>
+      <c r="L9" t="s">
+        <v>97</v>
+      </c>
       <c r="M9" t="s">
         <v>97</v>
       </c>
@@ -1223,7 +1241,22 @@
       <c r="G10">
         <v>16</v>
       </c>
+      <c r="H10">
+        <v>7500</v>
+      </c>
+      <c r="I10" t="s">
+        <v>125</v>
+      </c>
+      <c r="K10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L10" t="s">
+        <v>97</v>
+      </c>
       <c r="M10" t="s">
+        <v>97</v>
+      </c>
+      <c r="O10" t="s">
         <v>97</v>
       </c>
     </row>

--- a/masterProjectList.xlsx
+++ b/masterProjectList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\btmhess.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451AA615-3108-4DEA-ADE2-5490D5B8A2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1ED9FD-6B2D-4985-B5C3-3170A7349EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="131">
   <si>
     <t>Goldwing tractive battery</t>
   </si>
@@ -1004,28 +1004,28 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D5">
         <v>14</v>
       </c>
       <c r="E5">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="I5" t="s">
         <v>125</v>
@@ -1039,7 +1039,7 @@
       <c r="M5" t="s">
         <v>97</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>97</v>
       </c>
       <c r="P5" t="s">
@@ -1218,31 +1218,34 @@
       <c r="M9" t="s">
         <v>97</v>
       </c>
+      <c r="P9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D10">
         <v>25</v>
       </c>
       <c r="E10">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="I10" t="s">
         <v>125</v>
@@ -1256,7 +1259,10 @@
       <c r="M10" t="s">
         <v>97</v>
       </c>
-      <c r="O10" t="s">
+      <c r="N10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P10" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1282,6 +1288,12 @@
       <c r="G11">
         <v>400</v>
       </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>125</v>
+      </c>
       <c r="M11" t="s">
         <v>97</v>
       </c>
@@ -1308,6 +1320,12 @@
       <c r="G12">
         <v>32</v>
       </c>
+      <c r="H12">
+        <v>2000</v>
+      </c>
+      <c r="I12" t="s">
+        <v>125</v>
+      </c>
       <c r="M12" t="s">
         <v>97</v>
       </c>
@@ -1334,6 +1352,12 @@
       <c r="G13">
         <v>2</v>
       </c>
+      <c r="H13">
+        <v>1000</v>
+      </c>
+      <c r="I13" t="s">
+        <v>130</v>
+      </c>
       <c r="M13" t="s">
         <v>97</v>
       </c>
@@ -1363,6 +1387,9 @@
       <c r="H14" t="s">
         <v>127</v>
       </c>
+      <c r="I14" t="s">
+        <v>125</v>
+      </c>
       <c r="M14" t="s">
         <v>97</v>
       </c>
@@ -1389,6 +1416,9 @@
       <c r="G15">
         <v>16</v>
       </c>
+      <c r="I15" t="s">
+        <v>125</v>
+      </c>
       <c r="M15" t="s">
         <v>97</v>
       </c>
@@ -1415,6 +1445,12 @@
       <c r="G16">
         <v>3</v>
       </c>
+      <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16" t="s">
+        <v>128</v>
+      </c>
       <c r="M16" t="s">
         <v>97</v>
       </c>
@@ -1441,6 +1477,12 @@
       <c r="G17">
         <v>1040</v>
       </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
+        <v>128</v>
+      </c>
       <c r="M17" t="s">
         <v>97</v>
       </c>
@@ -1467,6 +1509,12 @@
       <c r="G18">
         <v>16</v>
       </c>
+      <c r="H18">
+        <v>450</v>
+      </c>
+      <c r="I18" t="s">
+        <v>126</v>
+      </c>
       <c r="M18" t="s">
         <v>97</v>
       </c>
@@ -1493,6 +1541,12 @@
       <c r="G19">
         <v>2</v>
       </c>
+      <c r="H19">
+        <v>30</v>
+      </c>
+      <c r="I19" t="s">
+        <v>130</v>
+      </c>
       <c r="M19" t="s">
         <v>97</v>
       </c>
@@ -1519,6 +1573,12 @@
       <c r="G20">
         <v>2</v>
       </c>
+      <c r="H20">
+        <v>25</v>
+      </c>
+      <c r="I20" t="s">
+        <v>125</v>
+      </c>
       <c r="M20" t="s">
         <v>97</v>
       </c>
@@ -1545,6 +1605,12 @@
       <c r="G21">
         <v>1</v>
       </c>
+      <c r="H21">
+        <v>250</v>
+      </c>
+      <c r="I21" t="s">
+        <v>130</v>
+      </c>
       <c r="M21" t="s">
         <v>97</v>
       </c>
@@ -1571,6 +1637,12 @@
       <c r="G22">
         <v>4</v>
       </c>
+      <c r="H22">
+        <v>150</v>
+      </c>
+      <c r="I22" t="s">
+        <v>130</v>
+      </c>
       <c r="M22" t="s">
         <v>97</v>
       </c>
@@ -1597,6 +1669,9 @@
       <c r="G23">
         <v>6</v>
       </c>
+      <c r="I23" t="s">
+        <v>125</v>
+      </c>
       <c r="M23" t="s">
         <v>97</v>
       </c>
@@ -1623,6 +1698,12 @@
       <c r="G24">
         <v>2</v>
       </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24" t="s">
+        <v>130</v>
+      </c>
       <c r="M24" t="s">
         <v>97</v>
       </c>
@@ -1649,6 +1730,12 @@
       <c r="G25">
         <v>3</v>
       </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" t="s">
+        <v>125</v>
+      </c>
       <c r="M25" t="s">
         <v>97</v>
       </c>
@@ -1675,6 +1762,12 @@
       <c r="G26">
         <v>2</v>
       </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26" t="s">
+        <v>130</v>
+      </c>
       <c r="M26" t="s">
         <v>97</v>
       </c>
@@ -1701,6 +1794,9 @@
       <c r="G27">
         <v>16</v>
       </c>
+      <c r="I27" t="s">
+        <v>128</v>
+      </c>
       <c r="M27" t="s">
         <v>97</v>
       </c>
@@ -1727,6 +1823,9 @@
       <c r="G28">
         <v>1</v>
       </c>
+      <c r="I28" t="s">
+        <v>128</v>
+      </c>
       <c r="M28" t="s">
         <v>97</v>
       </c>
@@ -1753,6 +1852,9 @@
       <c r="G29">
         <v>2</v>
       </c>
+      <c r="I29" t="s">
+        <v>128</v>
+      </c>
       <c r="M29" t="s">
         <v>97</v>
       </c>
@@ -1779,6 +1881,9 @@
       <c r="G30">
         <v>3</v>
       </c>
+      <c r="I30" t="s">
+        <v>125</v>
+      </c>
       <c r="M30" t="s">
         <v>97</v>
       </c>
@@ -1805,6 +1910,9 @@
       <c r="G31">
         <v>4</v>
       </c>
+      <c r="I31" t="s">
+        <v>130</v>
+      </c>
       <c r="M31" t="s">
         <v>97</v>
       </c>
@@ -1831,6 +1939,9 @@
       <c r="G32">
         <v>2</v>
       </c>
+      <c r="I32" t="s">
+        <v>128</v>
+      </c>
       <c r="M32" t="s">
         <v>97</v>
       </c>
@@ -1857,6 +1968,9 @@
       <c r="G33">
         <v>4</v>
       </c>
+      <c r="I33" t="s">
+        <v>130</v>
+      </c>
       <c r="M33" t="s">
         <v>97</v>
       </c>
@@ -1883,6 +1997,9 @@
       <c r="G34">
         <v>4</v>
       </c>
+      <c r="I34" t="s">
+        <v>125</v>
+      </c>
       <c r="M34" t="s">
         <v>97</v>
       </c>
@@ -1909,6 +2026,9 @@
       <c r="G35">
         <v>2</v>
       </c>
+      <c r="I35" t="s">
+        <v>128</v>
+      </c>
       <c r="M35" t="s">
         <v>97</v>
       </c>
@@ -1935,6 +2055,9 @@
       <c r="G36">
         <v>3</v>
       </c>
+      <c r="I36" t="s">
+        <v>125</v>
+      </c>
       <c r="M36" t="s">
         <v>97</v>
       </c>
@@ -1961,6 +2084,9 @@
       <c r="G37">
         <v>40</v>
       </c>
+      <c r="I37" t="s">
+        <v>130</v>
+      </c>
       <c r="M37" t="s">
         <v>97</v>
       </c>
@@ -1987,6 +2113,9 @@
       <c r="G38">
         <v>1</v>
       </c>
+      <c r="I38" t="s">
+        <v>128</v>
+      </c>
       <c r="M38" t="s">
         <v>97</v>
       </c>
@@ -2013,6 +2142,9 @@
       <c r="G39">
         <v>4</v>
       </c>
+      <c r="I39" t="s">
+        <v>130</v>
+      </c>
       <c r="M39" t="s">
         <v>97</v>
       </c>
@@ -2039,6 +2171,9 @@
       <c r="G40">
         <v>2</v>
       </c>
+      <c r="I40" t="s">
+        <v>125</v>
+      </c>
       <c r="M40" t="s">
         <v>97</v>
       </c>
@@ -2065,6 +2200,9 @@
       <c r="G41">
         <v>1</v>
       </c>
+      <c r="I41" t="s">
+        <v>130</v>
+      </c>
       <c r="M41" t="s">
         <v>97</v>
       </c>
@@ -2091,6 +2229,9 @@
       <c r="G42">
         <v>4</v>
       </c>
+      <c r="I42" t="s">
+        <v>130</v>
+      </c>
       <c r="M42" t="s">
         <v>97</v>
       </c>
@@ -2117,6 +2258,9 @@
       <c r="G43">
         <v>16</v>
       </c>
+      <c r="I43" t="s">
+        <v>130</v>
+      </c>
       <c r="M43" t="s">
         <v>97</v>
       </c>
@@ -2143,6 +2287,9 @@
       <c r="G44">
         <v>6</v>
       </c>
+      <c r="I44" t="s">
+        <v>125</v>
+      </c>
       <c r="M44" t="s">
         <v>97</v>
       </c>
@@ -2169,6 +2316,9 @@
       <c r="G45">
         <v>520</v>
       </c>
+      <c r="I45" t="s">
+        <v>126</v>
+      </c>
       <c r="M45" t="s">
         <v>97</v>
       </c>
@@ -2195,6 +2345,9 @@
       <c r="G46">
         <v>4</v>
       </c>
+      <c r="I46" t="s">
+        <v>128</v>
+      </c>
       <c r="M46" t="s">
         <v>97</v>
       </c>
@@ -2221,6 +2374,9 @@
       <c r="G47">
         <v>1</v>
       </c>
+      <c r="I47" t="s">
+        <v>125</v>
+      </c>
       <c r="M47" t="s">
         <v>97</v>
       </c>
@@ -2247,6 +2403,9 @@
       <c r="G48">
         <v>2</v>
       </c>
+      <c r="I48" t="s">
+        <v>128</v>
+      </c>
       <c r="M48" t="s">
         <v>97</v>
       </c>
@@ -2273,6 +2432,9 @@
       <c r="G49">
         <v>300</v>
       </c>
+      <c r="I49" t="s">
+        <v>125</v>
+      </c>
       <c r="M49" t="s">
         <v>97</v>
       </c>
@@ -2290,6 +2452,9 @@
       <c r="D50">
         <v>175</v>
       </c>
+      <c r="I50" t="s">
+        <v>128</v>
+      </c>
       <c r="M50" t="s">
         <v>97</v>
       </c>
@@ -2316,6 +2481,9 @@
       <c r="G51">
         <v>3</v>
       </c>
+      <c r="I51" t="s">
+        <v>125</v>
+      </c>
       <c r="M51" t="s">
         <v>97</v>
       </c>
@@ -2342,6 +2510,9 @@
       <c r="G52">
         <v>1</v>
       </c>
+      <c r="I52" t="s">
+        <v>125</v>
+      </c>
       <c r="M52" t="s">
         <v>97</v>
       </c>
@@ -2367,6 +2538,9 @@
       </c>
       <c r="G53">
         <v>24</v>
+      </c>
+      <c r="I53" t="s">
+        <v>126</v>
       </c>
       <c r="M53" t="s">
         <v>97</v>
